--- a/docs/Sprint 3/Clockify_graficas.xlsx
+++ b/docs/Sprint 3/Clockify_graficas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\ISPP-G8\ISPP-G8\docs\Sprint 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{761316E8-1A7B-49C5-AF7A-714FE93B4DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B337DF-AFBC-4329-8C3C-AEE66C9730AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1244,7 +1244,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{398F27BB-EB54-4A65-9942-6338CD177F3C}" type="CELLRANGE">
+                    <a:fld id="{9A804517-FF46-48C7-9410-FE78A09E5202}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1276,7 +1276,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{005208C4-62D9-47E0-A5C6-3640B952B8F1}" type="CELLRANGE">
+                    <a:fld id="{64900C9D-E584-4868-91A1-371D47273435}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1309,7 +1309,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{644870BE-2520-4485-8162-32A9D97A397C}" type="CELLRANGE">
+                    <a:fld id="{68D3E1D2-E42C-4F26-BA6C-F131932F4242}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1342,7 +1342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B5106BA7-3A8D-4D39-A492-FF624BFF070B}" type="CELLRANGE">
+                    <a:fld id="{32C2A694-06FA-4912-B981-011653074F61}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1375,7 +1375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B0295E40-6F6F-4AA0-999C-E8CE219360C6}" type="CELLRANGE">
+                    <a:fld id="{A4C00CC8-8665-490F-9EFD-9858B62B756E}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1408,7 +1408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{59107DB9-6022-40B2-B44F-B9512D6AB6DB}" type="CELLRANGE">
+                    <a:fld id="{1C8192ED-B699-4DF8-9A84-1BB689A8A0EF}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1441,7 +1441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0F21A7DE-0DBC-4CCF-A5BA-CA2B06BD4101}" type="CELLRANGE">
+                    <a:fld id="{C1FB38A1-E69A-45A8-AE44-FDF01E42F4B9}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1474,7 +1474,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD90DAFB-84D5-4519-89C6-9B3BFA545A41}" type="CELLRANGE">
+                    <a:fld id="{E6BA07BA-CFC1-4083-999F-4824C47F9E79}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1507,7 +1507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A619B4D-C4FC-45A9-91CC-16A5B3C14145}" type="CELLRANGE">
+                    <a:fld id="{9A802431-1B0E-4331-8E9C-D849AF48550F}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1540,7 +1540,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BD78A81E-CADA-4BC6-A5DD-1B66D28A2A1D}" type="CELLRANGE">
+                    <a:fld id="{80D396B5-1305-46BF-AC36-BB3D200B56BA}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1573,7 +1573,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09464F0E-D9C7-4CAD-BB8C-850D69824187}" type="CELLRANGE">
+                    <a:fld id="{7C94933E-3392-4330-8BD3-919C1622A00C}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1606,7 +1606,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CB22394-D207-4FF0-AB8E-0F3B535269F4}" type="CELLRANGE">
+                    <a:fld id="{ACA65CA7-B938-46F4-AD98-888978D7DD1C}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1639,7 +1639,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E1D88E49-B732-4F92-AD12-8F2B07FC9850}" type="CELLRANGE">
+                    <a:fld id="{6C8CC19F-6122-475F-9E9E-FF0547C1978D}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1672,7 +1672,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E12A2EC4-700B-4CE5-92F2-759C699FE183}" type="CELLRANGE">
+                    <a:fld id="{45AC2679-DDB3-4C70-A7F3-14BEC86B2919}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1705,7 +1705,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C2367951-2437-4122-B06A-140A2501173C}" type="CELLRANGE">
+                    <a:fld id="{F737DE59-45B0-4D0A-B657-C99BB9EE5B8F}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1738,7 +1738,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A2F5DFC-41C2-4CA3-AB6F-BEAB9ACF0DDF}" type="CELLRANGE">
+                    <a:fld id="{B4155E30-006C-43EA-9700-2C6A82A11C7E}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1771,7 +1771,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CDA3B6B7-092A-470F-9B9B-F4EE896FEC41}" type="CELLRANGE">
+                    <a:fld id="{AB033ED4-D438-48C8-A79B-7287DBF43F31}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1804,7 +1804,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3AC60075-E7D2-4F55-ADAC-B1BC45B6CDC3}" type="CELLRANGE">
+                    <a:fld id="{A67BF5FF-AC44-4048-9102-61C65668ECA8}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1837,7 +1837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{116D17D2-CE64-4694-AC3B-071BFEE5C34B}" type="CELLRANGE">
+                    <a:fld id="{949A65CE-6CF5-476B-A583-8E8CFEDC7966}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1870,7 +1870,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC9A838E-29EC-46FC-8DAF-98DEC324EAB1}" type="CELLRANGE">
+                    <a:fld id="{E8DB27D1-270E-4FBB-97C5-C4EBEFC13774}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/docs/Sprint 3/Clockify_graficas.xlsx
+++ b/docs/Sprint 3/Clockify_graficas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\ISPP-G8\ISPP-G8\docs\Sprint 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B337DF-AFBC-4329-8C3C-AEE66C9730AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D189101-A603-4175-9A1B-46B66C8A1C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -342,7 +342,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +364,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -535,6 +541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,7 +1251,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A804517-FF46-48C7-9410-FE78A09E5202}" type="CELLRANGE">
+                    <a:fld id="{506A3727-96AC-4F2E-AFED-E8B47A71F3EB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1276,7 +1283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{64900C9D-E584-4868-91A1-371D47273435}" type="CELLRANGE">
+                    <a:fld id="{11CD6B5F-0740-4E0F-B21F-4C825D2EFDB2}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1309,7 +1316,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68D3E1D2-E42C-4F26-BA6C-F131932F4242}" type="CELLRANGE">
+                    <a:fld id="{683C7A8C-3CFD-461F-A8D4-B6B0E427EDBB}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1342,7 +1349,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{32C2A694-06FA-4912-B981-011653074F61}" type="CELLRANGE">
+                    <a:fld id="{518F5EBA-BDC9-4646-A691-51D658C63128}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1375,7 +1382,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A4C00CC8-8665-490F-9EFD-9858B62B756E}" type="CELLRANGE">
+                    <a:fld id="{280532D2-3FEA-4692-8550-E6E5507D4014}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1408,7 +1415,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1C8192ED-B699-4DF8-9A84-1BB689A8A0EF}" type="CELLRANGE">
+                    <a:fld id="{E3546F22-D321-4FC2-BEAC-C19509E56FBF}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1441,7 +1448,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C1FB38A1-E69A-45A8-AE44-FDF01E42F4B9}" type="CELLRANGE">
+                    <a:fld id="{1642BA05-E504-4B07-BA6A-0CBEA16C7713}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1474,7 +1481,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E6BA07BA-CFC1-4083-999F-4824C47F9E79}" type="CELLRANGE">
+                    <a:fld id="{D4C11AAA-1EB1-4C59-9876-7E611FA132C9}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1507,7 +1514,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A802431-1B0E-4331-8E9C-D849AF48550F}" type="CELLRANGE">
+                    <a:fld id="{E6BD1BF7-9A10-46B9-A5D3-39D9CB66E99E}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1540,7 +1547,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80D396B5-1305-46BF-AC36-BB3D200B56BA}" type="CELLRANGE">
+                    <a:fld id="{5B147AE1-7254-40EC-B403-953EBE58FEDC}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1573,7 +1580,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C94933E-3392-4330-8BD3-919C1622A00C}" type="CELLRANGE">
+                    <a:fld id="{83E364C1-0ED8-41B5-87C1-3E06732C275E}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1606,7 +1613,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ACA65CA7-B938-46F4-AD98-888978D7DD1C}" type="CELLRANGE">
+                    <a:fld id="{7D444663-4359-4574-94AA-6C3B35944B1D}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1639,7 +1646,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6C8CC19F-6122-475F-9E9E-FF0547C1978D}" type="CELLRANGE">
+                    <a:fld id="{0D4411F0-DAB5-43B2-89A3-1C961FF1C7CC}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1672,7 +1679,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45AC2679-DDB3-4C70-A7F3-14BEC86B2919}" type="CELLRANGE">
+                    <a:fld id="{BA10F1AA-CB75-4620-A7C5-BD82C73D39E3}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1705,7 +1712,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F737DE59-45B0-4D0A-B657-C99BB9EE5B8F}" type="CELLRANGE">
+                    <a:fld id="{EFD7C593-C081-4763-88BC-E13C90540B96}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1738,7 +1745,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B4155E30-006C-43EA-9700-2C6A82A11C7E}" type="CELLRANGE">
+                    <a:fld id="{374DD6C2-3902-4CF9-9313-ACEA55C64D0B}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1771,7 +1778,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB033ED4-D438-48C8-A79B-7287DBF43F31}" type="CELLRANGE">
+                    <a:fld id="{1DACAE10-24B8-4BDE-A5BE-617E36C90794}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1804,7 +1811,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A67BF5FF-AC44-4048-9102-61C65668ECA8}" type="CELLRANGE">
+                    <a:fld id="{F934238D-E8B2-4F2E-938B-8262A0717555}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1837,7 +1844,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{949A65CE-6CF5-476B-A583-8E8CFEDC7966}" type="CELLRANGE">
+                    <a:fld id="{3A756AE9-5035-46AC-B739-389902BB2301}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1870,7 +1877,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E8DB27D1-270E-4FBB-97C5-C4EBEFC13774}" type="CELLRANGE">
+                    <a:fld id="{8BDECDE5-3D87-4599-ABFF-4EDB38ABAA69}" type="CELLRANGE">
                       <a:rPr lang="es-ES"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2418,9 +2425,7 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -3532,6 +3537,287 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>391886</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>48986</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectángulo 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFC25280-6026-CC8F-42C8-665B2874A59B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12834257" y="5720443"/>
+          <a:ext cx="3450772" cy="1110343"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+              <a:alpha val="90000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>604157</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>391886</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectángulo 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC3C177-B186-91EB-CEF1-2DAD872551E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12839700" y="4327071"/>
+          <a:ext cx="3445329" cy="1382486"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+              <a:alpha val="90000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>440871</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectángulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C37F0B11-0B5A-228C-7EA1-186F0D79EE37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11457214" y="4327071"/>
+          <a:ext cx="1377043" cy="1387929"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+              <a:alpha val="90000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>440871</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>593271</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>48986</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectángulo 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58998A3B-DD07-F266-3F55-C55C93280DB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11457214" y="5715000"/>
+          <a:ext cx="1371600" cy="1115786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000">
+            <a:alpha val="90000"/>
+          </a:srgbClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -3568,16 +3854,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101046</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>124446</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>581024</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>668405</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>5384</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3868,7 +4154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -4395,7 +4681,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
@@ -4423,8 +4709,18 @@
       <c r="H17" s="19" t="s">
         <v>75</v>
       </c>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -4452,8 +4748,18 @@
       <c r="H18" s="19" t="s">
         <v>81</v>
       </c>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -4481,8 +4787,17 @@
       <c r="H19" s="19" t="s">
         <v>76</v>
       </c>
+      <c r="I19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
@@ -4510,8 +4825,18 @@
       <c r="H20" s="19" t="s">
         <v>77</v>
       </c>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -4539,8 +4864,18 @@
       <c r="H21" s="19" t="s">
         <v>78</v>
       </c>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4554,8 +4889,18 @@
       <c r="F22" s="1"/>
       <c r="G22" s="21"/>
       <c r="H22" s="1"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="12" t="s">
         <v>40</v>
@@ -4577,8 +4922,18 @@
         <v>10.764973261382725</v>
       </c>
       <c r="H23" s="1"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="13" t="s">
         <v>41</v>
@@ -4597,8 +4952,18 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4612,8 +4977,18 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4627,8 +5002,18 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4642,8 +5027,18 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4652,8 +5047,18 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4662,8 +5067,18 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -4672,9 +5087,137 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+    </row>
+    <row r="33" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E33" s="6"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+    </row>
+    <row r="34" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+    </row>
+    <row r="35" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+    </row>
+    <row r="36" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+    </row>
+    <row r="37" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+    </row>
+    <row r="38" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+    </row>
+    <row r="39" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="22"/>
+    </row>
+    <row r="40" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22"/>
+      <c r="R40" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
